--- a/resources/app-mry/content/pricing/pricing_usd.xlsx
+++ b/resources/app-mry/content/pricing/pricing_usd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Mehery Website\mehery.site\resources\app-mry\content\pricing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6288D71-ABA1-4DB1-820A-F7DFB0AAF0E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DC246C-E12E-489E-8ABE-2A710684CE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="78">
   <si>
     <t>name</t>
   </si>
@@ -45,9 +45,6 @@
     <t>fees.quaterly</t>
   </si>
   <si>
-    <t>mfees.waba</t>
-  </si>
-  <si>
     <t>mfees.social</t>
   </si>
   <si>
@@ -237,18 +234,12 @@
     <t>$384</t>
   </si>
   <si>
-    <t>$0</t>
-  </si>
-  <si>
     <t>$25</t>
   </si>
   <si>
     <t>On Req</t>
   </si>
   <si>
-    <t>Max 10/day</t>
-  </si>
-  <si>
     <t>FREE</t>
   </si>
   <si>
@@ -259,6 +250,15 @@
   </si>
   <si>
     <t>$399</t>
+  </si>
+  <si>
+    <t>mfees.wabaUtil</t>
+  </si>
+  <si>
+    <t>mfees.wabaMarketing</t>
+  </si>
+  <si>
+    <t>10/day</t>
   </si>
 </sst>
 </file>
@@ -630,10 +630,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -653,428 +653,446 @@
         <v>4</v>
       </c>
       <c r="G1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
-        <v>14</v>
-      </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>19</v>
       </c>
       <c r="T1" t="s">
         <v>18</v>
       </c>
       <c r="U1" t="s">
+        <v>17</v>
+      </c>
+      <c r="V1" t="s">
+        <v>19</v>
+      </c>
+      <c r="W1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>23</v>
       </c>
+      <c r="B2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="V2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="W2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y2" s="3" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="M2">
+      <c r="D3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" t="s">
+        <v>72</v>
+      </c>
+      <c r="G3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" t="s">
+        <v>41</v>
+      </c>
+      <c r="L3" t="s">
+        <v>42</v>
+      </c>
+      <c r="M3" t="s">
+        <v>43</v>
+      </c>
+      <c r="N3">
         <v>1</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" t="s">
-        <v>44</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3" t="s">
-        <v>51</v>
-      </c>
       <c r="O3" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="P3" t="s">
         <v>54</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="s">
+        <v>53</v>
+      </c>
+      <c r="R3">
         <v>1</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
+        <v>51</v>
+      </c>
+      <c r="T3" t="s">
+        <v>64</v>
+      </c>
+      <c r="U3" t="s">
+        <v>65</v>
+      </c>
+      <c r="V3" t="s">
+        <v>69</v>
+      </c>
+      <c r="W3" t="s">
+        <v>51</v>
+      </c>
+      <c r="X3" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N4">
+        <v>5</v>
+      </c>
+      <c r="O4" t="s">
         <v>52</v>
       </c>
-      <c r="S3" t="s">
-        <v>65</v>
-      </c>
-      <c r="T3" t="s">
+      <c r="P4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>56</v>
+      </c>
+      <c r="R4">
+        <v>2</v>
+      </c>
+      <c r="S4" t="s">
         <v>66</v>
       </c>
-      <c r="U3" t="s">
-        <v>71</v>
-      </c>
-      <c r="V3" t="s">
-        <v>52</v>
-      </c>
-      <c r="W3" t="s">
-        <v>72</v>
-      </c>
-      <c r="X3" t="s">
-        <v>72</v>
+      <c r="T4" t="s">
+        <v>67</v>
+      </c>
+      <c r="U4" t="s">
+        <v>68</v>
+      </c>
+      <c r="V4" t="s">
+        <v>69</v>
+      </c>
+      <c r="W4" t="s">
+        <v>51</v>
+      </c>
+      <c r="X4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>28</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="D5" t="s">
         <v>35</v>
       </c>
-      <c r="G4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="E5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" t="s">
         <v>47</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K5" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" t="s">
         <v>45</v>
       </c>
-      <c r="K4" t="s">
-        <v>46</v>
-      </c>
-      <c r="L4" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4">
-        <v>5</v>
-      </c>
-      <c r="N4" t="s">
-        <v>53</v>
-      </c>
-      <c r="O4" t="s">
-        <v>56</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="M5" t="s">
+        <v>31</v>
+      </c>
+      <c r="N5">
+        <v>7</v>
+      </c>
+      <c r="O5" t="s">
         <v>57</v>
       </c>
-      <c r="Q4">
-        <v>2</v>
-      </c>
-      <c r="R4" t="s">
+      <c r="P5" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>62</v>
+      </c>
+      <c r="R5">
+        <v>3</v>
+      </c>
+      <c r="S5" t="s">
+        <v>66</v>
+      </c>
+      <c r="T5" t="s">
         <v>67</v>
       </c>
-      <c r="S4" t="s">
+      <c r="U5" t="s">
         <v>68</v>
       </c>
-      <c r="T4" t="s">
+      <c r="V5" t="s">
         <v>69</v>
       </c>
-      <c r="U4" t="s">
-        <v>71</v>
-      </c>
-      <c r="V4" t="s">
-        <v>52</v>
-      </c>
-      <c r="W4" t="s">
-        <v>32</v>
-      </c>
-      <c r="X4" t="s">
-        <v>32</v>
+      <c r="W5" t="s">
+        <v>51</v>
+      </c>
+      <c r="X5" t="s">
+        <v>31</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>29</v>
       </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" t="s">
         <v>37</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F6" t="s">
         <v>38</v>
       </c>
-      <c r="G5" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" t="s">
-        <v>46</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" t="s">
+        <v>47</v>
+      </c>
+      <c r="K6" t="s">
         <v>48</v>
       </c>
-      <c r="J5" t="s">
+      <c r="L6" t="s">
         <v>45</v>
       </c>
-      <c r="K5" t="s">
-        <v>46</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5">
-        <v>7</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="M6" t="s">
+        <v>49</v>
+      </c>
+      <c r="N6">
+        <v>10</v>
+      </c>
+      <c r="O6" t="s">
         <v>58</v>
       </c>
-      <c r="O5" t="s">
-        <v>62</v>
-      </c>
-      <c r="P5" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q5">
-        <v>3</v>
-      </c>
-      <c r="R5" t="s">
-        <v>67</v>
-      </c>
-      <c r="S5" t="s">
-        <v>68</v>
-      </c>
-      <c r="T5" t="s">
+      <c r="P6" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>60</v>
+      </c>
+      <c r="R6">
+        <v>8</v>
+      </c>
+      <c r="S6" t="s">
+        <v>58</v>
+      </c>
+      <c r="T6" t="s">
+        <v>59</v>
+      </c>
+      <c r="U6" t="s">
+        <v>60</v>
+      </c>
+      <c r="V6" t="s">
         <v>69</v>
       </c>
-      <c r="U5" t="s">
-        <v>71</v>
-      </c>
-      <c r="V5" t="s">
-        <v>52</v>
-      </c>
-      <c r="W5" t="s">
-        <v>32</v>
-      </c>
-      <c r="X5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>77</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" t="s">
-        <v>46</v>
-      </c>
-      <c r="H6" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" t="s">
-        <v>50</v>
-      </c>
-      <c r="M6">
-        <v>10</v>
-      </c>
-      <c r="N6" t="s">
-        <v>59</v>
-      </c>
-      <c r="O6" t="s">
-        <v>60</v>
-      </c>
-      <c r="P6" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q6">
-        <v>8</v>
-      </c>
-      <c r="R6" t="s">
+      <c r="W6" t="s">
+        <v>51</v>
+      </c>
+      <c r="X6" t="s">
         <v>70</v>
       </c>
-      <c r="S6" t="s">
+      <c r="Y6" t="s">
         <v>70</v>
-      </c>
-      <c r="T6" t="s">
-        <v>70</v>
-      </c>
-      <c r="U6" t="s">
-        <v>71</v>
-      </c>
-      <c r="V6" t="s">
-        <v>52</v>
-      </c>
-      <c r="W6" t="s">
-        <v>72</v>
-      </c>
-      <c r="X6" t="s">
-        <v>72</v>
       </c>
     </row>
   </sheetData>
